--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.29165955191778</v>
+        <v>9.472394677186641</v>
       </c>
       <c r="D2" t="n">
-        <v>47.33963573065504</v>
+        <v>7.692690806231444</v>
       </c>
       <c r="E2" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F2" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.55507673403515</v>
+        <v>8.377699969280712</v>
       </c>
       <c r="D3" t="n">
-        <v>51.64578009440509</v>
+        <v>8.392439265340828</v>
       </c>
       <c r="E3" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F3" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.44408822242148</v>
+        <v>8.359664336143492</v>
       </c>
       <c r="D4" t="n">
-        <v>52.86278791488899</v>
+        <v>8.590203036169461</v>
       </c>
       <c r="E4" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F4" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.30526378334115</v>
+        <v>7.037105364792938</v>
       </c>
       <c r="D5" t="n">
-        <v>34.2874976388051</v>
+        <v>5.571718366305829</v>
       </c>
       <c r="E5" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F5" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.85582654956419</v>
+        <v>8.751571814304182</v>
       </c>
       <c r="D6" t="n">
-        <v>57.79352359071611</v>
+        <v>9.391447583491368</v>
       </c>
       <c r="E6" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F6" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.53625633568932</v>
+        <v>9.024641654549516</v>
       </c>
       <c r="D7" t="n">
-        <v>61.58741545795316</v>
+        <v>10.00795501191739</v>
       </c>
       <c r="E7" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F7" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.20630020724348</v>
+        <v>4.421023783677065</v>
       </c>
       <c r="D8" t="n">
-        <v>22.43368928975165</v>
+        <v>3.645474509584643</v>
       </c>
       <c r="E8" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F8" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.48207080378077</v>
+        <v>7.390836505614375</v>
       </c>
       <c r="D9" t="n">
-        <v>51.57572976450682</v>
+        <v>8.381056086732357</v>
       </c>
       <c r="E9" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F9" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.06226145004801</v>
+        <v>8.622617485632802</v>
       </c>
       <c r="D10" t="n">
-        <v>59.48274846047902</v>
+        <v>9.665946624827841</v>
       </c>
       <c r="E10" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F10" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.39648237595081</v>
+        <v>2.339428386092006</v>
       </c>
       <c r="D11" t="n">
-        <v>7.77962490575289</v>
+        <v>1.264189047184845</v>
       </c>
       <c r="E11" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F11" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.18661144336864</v>
+        <v>7.342824359547405</v>
       </c>
       <c r="D12" t="n">
-        <v>52.04791632420501</v>
+        <v>8.457786402683315</v>
       </c>
       <c r="E12" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F12" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.72305253662723</v>
+        <v>5.154996037201926</v>
       </c>
       <c r="D13" t="n">
-        <v>38.45427168220559</v>
+        <v>6.248819148358408</v>
       </c>
       <c r="E13" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F13" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>37.13695903681732</v>
+        <v>6.034755843482816</v>
       </c>
       <c r="D14" t="n">
-        <v>15.61591860043363</v>
+        <v>2.537586772570465</v>
       </c>
       <c r="E14" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F14" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.63807701850177</v>
+        <v>6.441187515506537</v>
       </c>
       <c r="D15" t="n">
-        <v>43.92553422254237</v>
+        <v>7.137899311163135</v>
       </c>
       <c r="E15" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F15" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.99636527949863</v>
+        <v>6.174409357918528</v>
       </c>
       <c r="D16" t="n">
-        <v>35.88975588338499</v>
+        <v>5.83208533105006</v>
       </c>
       <c r="E16" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F16" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>41.9469237105958</v>
+        <v>6.816375102971818</v>
       </c>
       <c r="D17" t="n">
-        <v>3.377195946613465</v>
+        <v>0.5487943413246882</v>
       </c>
       <c r="E17" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F17" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>49.30290143895886</v>
+        <v>8.011721483830815</v>
       </c>
       <c r="D18" t="n">
-        <v>51.61544540195521</v>
+        <v>8.387509877817722</v>
       </c>
       <c r="E18" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F18" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>59.52368212446403</v>
+        <v>9.672598345225405</v>
       </c>
       <c r="D19" t="n">
-        <v>26.47412114990464</v>
+        <v>4.302044686859504</v>
       </c>
       <c r="E19" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F19" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>60.00923109058214</v>
+        <v>9.751500052219598</v>
       </c>
       <c r="D20" t="n">
-        <v>33.54318233109029</v>
+        <v>5.450767128802172</v>
       </c>
       <c r="E20" t="n">
-        <v>11.58891077468517</v>
+        <v>1.88319800088634</v>
       </c>
       <c r="F20" t="n">
-        <v>17.01052753393634</v>
+        <v>2.764210724264655</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
